--- a/DAY 1/Projita_Kar_Manual_Testing_Report.xlsx
+++ b/DAY 1/Projita_Kar_Manual_Testing_Report.xlsx
@@ -1,16 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29912"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29917"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D1739B0C-57E3-4B69-9D73-3D80D9893F79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C05D45DC-3968-4044-8E1C-24820F7972E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="3" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="User_Story" sheetId="1" r:id="rId1"/>
     <sheet name="Test_Scenario" sheetId="2" r:id="rId2"/>
     <sheet name="Test_Cases" sheetId="3" r:id="rId3"/>
+    <sheet name="Defect Report" sheetId="4" r:id="rId4"/>
+    <sheet name="RTM" sheetId="5" r:id="rId5"/>
+    <sheet name="Summary" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -33,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="343">
   <si>
     <t>Issue Type</t>
   </si>
@@ -47,7 +50,7 @@
     <t>Epic 1</t>
   </si>
   <si>
-    <t>NoBroker Home Services – Post Residential Rental Property</t>
+    <t>NoBroker – Post Your Property: Rental Residential Property</t>
   </si>
   <si>
     <t>High</t>
@@ -56,261 +59,278 @@
     <t>Story 1</t>
   </si>
   <si>
+    <t>User wants to navigate to "Post Your Property" Page from Homepage</t>
+  </si>
+  <si>
+    <t>Sub Story 1</t>
+  </si>
+  <si>
+    <t>Verify “Post Your Property” option visibility on Homepage</t>
+  </si>
+  <si>
+    <t>Sub Story 2</t>
+  </si>
+  <si>
+    <t>Verify navigation to Post Your Property page on click</t>
+  </si>
+  <si>
+    <t>Story 2</t>
+  </si>
+  <si>
+    <t>User wants to select Property Type and Ad Type on Post Property Page</t>
+  </si>
+  <si>
+    <t>Verify Residential property type selection</t>
+  </si>
+  <si>
+    <t>Verify Rent ad type selection</t>
+  </si>
+  <si>
+    <t>Sub Story 3</t>
+  </si>
+  <si>
+    <t>Verify location (city) selection functionality</t>
+  </si>
+  <si>
+    <t>Story 3</t>
+  </si>
+  <si>
+    <t>User wants to enter Property Details for Residential Rental Property</t>
+  </si>
+  <si>
+    <t>Verify apartment type and BHK selection</t>
+  </si>
+  <si>
+    <t>Verify floor and property age selection</t>
+  </si>
+  <si>
+    <t>Verify facing and built-up area input</t>
+  </si>
+  <si>
+    <t>Sub Story 4</t>
+  </si>
+  <si>
+    <t>Verify mandatory field validation and Save &amp; Continue functionality</t>
+  </si>
+  <si>
+    <t>Story 4</t>
+  </si>
+  <si>
+    <t>User wants to enter Locality Details on Property Posting Page</t>
+  </si>
+  <si>
+    <t>Verify city and locality selection</t>
+  </si>
+  <si>
+    <t>Verify landmark/street input functionality</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>Verify map selection and Save &amp; Continue</t>
+  </si>
+  <si>
+    <t>Story 5</t>
+  </si>
+  <si>
+    <t>User wants to enter Rental Details on Property Posting Page</t>
+  </si>
+  <si>
+    <t>Verify rent and deposit input</t>
+  </si>
+  <si>
+    <t>Verify property availability and maintenance details</t>
+  </si>
+  <si>
+    <t>Verify tenant preferences, furnishing, and parking selection</t>
+  </si>
+  <si>
+    <t>Verify description input and Save &amp; Continue</t>
+  </si>
+  <si>
+    <t>Story 6</t>
+  </si>
+  <si>
+    <t>User wants to enter Additional Property Details</t>
+  </si>
+  <si>
+    <t>Verify bathroom, balcony, and water supply inputs</t>
+  </si>
+  <si>
+    <t>Verify property preferences (pet allowed, gym, non-veg, gated security)</t>
+  </si>
+  <si>
+    <t>Verify contact details and property condition inputs</t>
+  </si>
+  <si>
+    <t>Verify amenities selection and directions input</t>
+  </si>
+  <si>
+    <t>Story 7</t>
+  </si>
+  <si>
+    <t>User wants to upload Property Photos and Videos</t>
+  </si>
+  <si>
+    <t>Verify photo and video upload functionality</t>
+  </si>
+  <si>
+    <t>Verify alternative upload options (phone/email)</t>
+  </si>
+  <si>
+    <t>Story 8</t>
+  </si>
+  <si>
+    <t>User wants to set Property Visit Schedule and Availability</t>
+  </si>
+  <si>
+    <t>Verify availability selection (Everyday/Weekday/Weekend)</t>
+  </si>
+  <si>
+    <t>Verify time schedule selection (start time, end time, all-day option)</t>
+  </si>
+  <si>
+    <t>Story 9</t>
+  </si>
+  <si>
+    <t>User wants to verify Property Posting Success and Next Actions</t>
+  </si>
+  <si>
+    <t>Verify success message and listing confirmation</t>
+  </si>
+  <si>
+    <t>Verify Edit and Preview Listing functionality</t>
+  </si>
+  <si>
+    <t>Verify additional actions (list another property / sale option)</t>
+  </si>
+  <si>
+    <t>Story 10</t>
+  </si>
+  <si>
+    <t>User wants to verify Property Preview Functionality</t>
+  </si>
+  <si>
+    <t>Verify property details are displayed correctly in preview</t>
+  </si>
+  <si>
+    <t>TestScenarioID</t>
+  </si>
+  <si>
+    <t>Requirement ID</t>
+  </si>
+  <si>
+    <t>Test Scenario Description</t>
+  </si>
+  <si>
+    <t>Type of Testing</t>
+  </si>
+  <si>
+    <t>Possible No. of TestCases</t>
+  </si>
+  <si>
+    <t>Test Case Details</t>
+  </si>
+  <si>
+    <t>TS_NoBroker_01</t>
+  </si>
+  <si>
+    <t>REQ_NoBroker_01</t>
+  </si>
+  <si>
     <t>Navigate to Post Your Property Page from Homepage</t>
   </si>
   <si>
-    <t>Sub Story 1</t>
-  </si>
-  <si>
-    <t>Verify “Post Your Property” option visibility on Homepage</t>
-  </si>
-  <si>
-    <t>Sub Story 2</t>
-  </si>
-  <si>
-    <t>Verify navigation to Post Your Property page on click</t>
-  </si>
-  <si>
-    <t>Story 2</t>
+    <t>Functional Testing</t>
+  </si>
+  <si>
+    <t>1. Verify navigation on clicking “Post Your Property”.
+2. Verify behavior when user clicks multiple times.</t>
+  </si>
+  <si>
+    <t>TS_NoBroker_02</t>
+  </si>
+  <si>
+    <t>REQ_NoBroker_02</t>
   </si>
   <si>
     <t>Select Property Type and Ad Type on Post Property Page</t>
   </si>
   <si>
-    <t>Verify Residential property type selection</t>
-  </si>
-  <si>
-    <t>Verify Rent ad type selection</t>
-  </si>
-  <si>
-    <t>Sub Story 3</t>
-  </si>
-  <si>
-    <t>Verify location (city) selection functionality</t>
-  </si>
-  <si>
-    <t>Story 3</t>
+    <t>1. Verify selection of Residential property type, Rent ad type, and city/location allows user to proceed.
+2. Verify city/location dropdown selection functionality
+3. Verify validation when city is not selected.</t>
+  </si>
+  <si>
+    <t>TS_NoBroker_03</t>
+  </si>
+  <si>
+    <t>REQ_NoBroker_03</t>
   </si>
   <si>
     <t>Enter Property Details for Residential Rental Property</t>
   </si>
   <si>
-    <t>Verify apartment type and BHK selection</t>
-  </si>
-  <si>
-    <t>Verify floor and property age selection</t>
-  </si>
-  <si>
-    <t>Verify facing and built-up area input</t>
-  </si>
-  <si>
-    <t>Sub Story 4</t>
-  </si>
-  <si>
-    <t>Verify mandatory field validation and Save &amp; Continue functionality</t>
-  </si>
-  <si>
-    <t>Story 4</t>
+    <t>1. Verify selection of apartment type, BHK, floor, facing, and property age.
+2. Validate Property Details form with valid inputs
+3. Verify validation when mandatory fields are empty.
+4. Verify validation for exceeding built-up area limit.
+5. Verify validation for insufficient built-up area based on BHK.</t>
+  </si>
+  <si>
+    <t>TS_NoBroker_04</t>
+  </si>
+  <si>
+    <t>REQ_NoBroker_04</t>
   </si>
   <si>
     <t>Enter Locality Details on Property Posting Page</t>
   </si>
   <si>
-    <t>Verify city and locality selection</t>
-  </si>
-  <si>
-    <t>Verify landmark/street input functionality</t>
-  </si>
-  <si>
-    <t>Medium</t>
-  </si>
-  <si>
-    <t>Verify map selection and Save &amp; Continue</t>
-  </si>
-  <si>
-    <t>Story 5</t>
+    <t>1. Verify city and locality dropdown selections are functional.
+2. Validate Locality Details form with valid inputs
+3. Verify validation when locality/location is not selected.
+4. Verify mismatch between city and locality selection.</t>
+  </si>
+  <si>
+    <t>TS_NoBroker_05</t>
+  </si>
+  <si>
+    <t>REQ_NoBroker_05</t>
   </si>
   <si>
     <t>Enter Rental Details on Property Posting Page</t>
   </si>
   <si>
-    <t>Verify rent and deposit input</t>
-  </si>
-  <si>
-    <t>Verify property availability and maintenance details</t>
-  </si>
-  <si>
-    <t>Verify tenant preferences, furnishing, and parking selection</t>
-  </si>
-  <si>
-    <t>Verify description input and Save &amp; Continue</t>
-  </si>
-  <si>
-    <t>Story 6</t>
-  </si>
-  <si>
-    <t>Enter Additional Property Details</t>
-  </si>
-  <si>
-    <t>Verify bathroom, balcony, and water supply inputs</t>
-  </si>
-  <si>
-    <t>Verify property preferences (pet allowed, gym, non-veg, gated security)</t>
-  </si>
-  <si>
-    <t>Verify contact details and property condition inputs</t>
-  </si>
-  <si>
-    <t>Verify amenities selection and directions input</t>
-  </si>
-  <si>
-    <t>Story 7</t>
+    <t>1. Verify dropdown selections in Rental Details.
+2. Verify availability date selection (Calendar).
+3. Validate Rental Details form with valid inputs.
+4. Verify validation when deposit is less than rent.</t>
+  </si>
+  <si>
+    <t>TS_NoBroker_06</t>
+  </si>
+  <si>
+    <t>REQ_NoBroker_06</t>
+  </si>
+  <si>
+    <t>Enter Amenities and Additional Property Details</t>
+  </si>
+  <si>
+    <t>1. Verify counter and dropdown selections.
+2. Verify toggle and other dropdown selections.
+3. Validate Amenities form with valid inputs.
+4. Verify validation when mandatory fields are not selected.</t>
+  </si>
+  <si>
+    <t>TS_NoBroker_07</t>
+  </si>
+  <si>
+    <t>REQ_NoBroker_07</t>
   </si>
   <si>
     <t>Upload Property Photos and Videos</t>
-  </si>
-  <si>
-    <t>Verify photo and video upload functionality</t>
-  </si>
-  <si>
-    <t>Verify alternative upload options (phone/email)</t>
-  </si>
-  <si>
-    <t>Story 8</t>
-  </si>
-  <si>
-    <t>Set Property Visit Schedule and Availability</t>
-  </si>
-  <si>
-    <t>Verify availability selection (Everyday/Weekday/Weekend)</t>
-  </si>
-  <si>
-    <t>Verify time schedule selection (start time, end time, all-day option)</t>
-  </si>
-  <si>
-    <t>Story 9</t>
-  </si>
-  <si>
-    <t>Verify Property Posting Success and Next Actions</t>
-  </si>
-  <si>
-    <t>Verify success message and listing confirmation</t>
-  </si>
-  <si>
-    <t>Verify Edit and Preview Listing functionality</t>
-  </si>
-  <si>
-    <t>Verify additional actions (list another property / sale option)</t>
-  </si>
-  <si>
-    <t>Story 10</t>
-  </si>
-  <si>
-    <t>Verify Property Preview Functionality</t>
-  </si>
-  <si>
-    <t>Verify property details are displayed correctly in preview</t>
-  </si>
-  <si>
-    <t>TestScenarioID</t>
-  </si>
-  <si>
-    <t>Requirement ID</t>
-  </si>
-  <si>
-    <t>Test Scenario Description</t>
-  </si>
-  <si>
-    <t>Type of Testing</t>
-  </si>
-  <si>
-    <t>Possible No. of TestCases</t>
-  </si>
-  <si>
-    <t>Test Case Details</t>
-  </si>
-  <si>
-    <t>TS_NoBroker_01</t>
-  </si>
-  <si>
-    <t>REQ_NoBroker_01</t>
-  </si>
-  <si>
-    <t>Functional Testing</t>
-  </si>
-  <si>
-    <t>1. Verify navigation on clicking “Post Your Property”.
-2. Verify visibility of “Post Your Property” option.
-3. Verify behavior when user clicks multiple times.</t>
-  </si>
-  <si>
-    <t>TS_NoBroker_02</t>
-  </si>
-  <si>
-    <t>REQ_NoBroker_02</t>
-  </si>
-  <si>
-    <t>1. Verify Residential and Rent selection.
-2. Verify city/location dropdown is functional and searchable.
-3. Verify validation when property type is not selected.
-4. Verify validation when city is not selected.</t>
-  </si>
-  <si>
-    <t>TS_NoBroker_03</t>
-  </si>
-  <si>
-    <t>REQ_NoBroker_03</t>
-  </si>
-  <si>
-    <t>1. Verify selection of apartment type, BHK, floor, and property age.
-2. Verify built-up area and facing input.
-3. Verify validation when mandatory fields are empty.
-4. Verify validation when invalid data is entered.</t>
-  </si>
-  <si>
-    <t>TS_NoBroker_04</t>
-  </si>
-  <si>
-    <t>REQ_NoBroker_04</t>
-  </si>
-  <si>
-    <t>1. Verify city and locality dropdown selections are functional.
-2. Verify landmark/street name input field accepts text input.
-3. Verify map pin can be dropped/moved to select location.
-4. Verify validation when locality/location is not selected.</t>
-  </si>
-  <si>
-    <t>TS_NoBroker_05</t>
-  </si>
-  <si>
-    <t>REQ_NoBroker_05</t>
-  </si>
-  <si>
-    <t>1. Verify rent and deposit input accepts valid numeric values only.
-2. Verify property availability date selection.
-3. Verify tenant preference, furnishing, parking, and maintenance selection.
-4. Verify validation when invalid input is entered.</t>
-  </si>
-  <si>
-    <t>TS_NoBroker_06</t>
-  </si>
-  <si>
-    <t>REQ_NoBroker_06</t>
-  </si>
-  <si>
-    <t>Enter Amenities and Additional Property Details</t>
-  </si>
-  <si>
-    <t>1. Verify bathroom, balcony, and water supply inputs.
-2. Verify property preferences (pet allowed, gym, non-veg, gated security).
-3. Verify amenities selection functionality.
-4. Verify validation when mandatory fields are not selected.</t>
-  </si>
-  <si>
-    <t>TS_NoBroker_07</t>
-  </si>
-  <si>
-    <t>REQ_NoBroker_07</t>
   </si>
   <si>
     <t>1. Verify photo upload accepts valid formats (JPG, PNG).
@@ -324,10 +344,12 @@
     <t>REQ_NoBroker_08</t>
   </si>
   <si>
-    <t>1. Verify availability selection (Everyday / Weekday / Weekend).
-2. Verify start time and end time selection.
-3. Verify “All Day” option functionality.
-4. Verify validation when time or availability is not selected.</t>
+    <t>Set Property Visit Schedule and Availability</t>
+  </si>
+  <si>
+    <t>1. Verify availability selection (Everyday / Weekday / Weekend) along with start and end time selection.
+2. Validate Visit Schedule form with valid inputs.
+3. Verify validation when time or availability is not selected.</t>
   </si>
   <si>
     <t>TS_NoBroker_09</t>
@@ -341,8 +363,7 @@
   <si>
     <t>1. Verify success message is displayed upon property submission.
 2. Verify user can edit the listing from the success screen.
-3. Verify 'Preview Listing' shows all entered property details accurately.
-4. Verify option to list another property or switch to sale is available.</t>
+3. Verify 'Preview Listing' shows all entered property details accurately.</t>
   </si>
   <si>
     <t>Test Case ID</t>
@@ -351,7 +372,7 @@
     <t>Test Scenario</t>
   </si>
   <si>
-    <t>Preconditions</t>
+    <t>Precondition</t>
   </si>
   <si>
     <t>Test Condition</t>
@@ -360,35 +381,861 @@
     <t>Test Case Steps</t>
   </si>
   <si>
-    <t xml:space="preserve">Test Data </t>
+    <t>Test Data</t>
   </si>
   <si>
     <t>Expected Result</t>
   </si>
   <si>
-    <t>Actual Result Iteration 1</t>
-  </si>
-  <si>
-    <t>Status Iteration 1</t>
-  </si>
-  <si>
-    <t>Actual Result Iteration 2</t>
-  </si>
-  <si>
-    <t>Status Iteration 2</t>
+    <t>Actual Result
+Iteration 1</t>
+  </si>
+  <si>
+    <t>Status
+Iteration 1</t>
+  </si>
+  <si>
+    <t>Actual Result Iteration 2
+(to be updated only if test case failed in Iteration 1)</t>
+  </si>
+  <si>
+    <t>Status Iteration 2
+(to be updated only if test case failed in Iteration 1)</t>
   </si>
   <si>
     <t>Comments</t>
   </si>
   <si>
     <t>Req: Reference</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_01</t>
+  </si>
+  <si>
+    <t>1. User has opened NoBroker website
+2. User is on the Homepage</t>
+  </si>
+  <si>
+    <t>Verify that clicking 'Post Your Property' navigates to the correct page</t>
+  </si>
+  <si>
+    <t>1. Open browser and navigate to "https://www.nobroker.in"
+2. Locate the “Post Your Property” option on the homepage (header/menu)
+3. Click on it
+4. Observe the page loaded</t>
+  </si>
+  <si>
+    <t>URL: https://www.nobroker.in
+Browser: Chrome (latest)</t>
+  </si>
+  <si>
+    <t>User is redirected to the “Post Your Property” page and the page loads successfully without errors</t>
+  </si>
+  <si>
+    <t>User is redirected to the Post Your Property page and the page loads successfully without errors</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t> </t>
+  </si>
+  <si>
+    <t>TC_NoBroker_02</t>
+  </si>
+  <si>
+    <t>Verify behavior when user clicks 'Post Your Property' multiple times</t>
+  </si>
+  <si>
+    <t>1. Open browser and navigate to "https://www.nobroker.in"
+2. Click 'Post Your Property' button rapidly multiple times
+3. Observe the response</t>
+  </si>
+  <si>
+    <t>URL: https://www.nobroker.in</t>
+  </si>
+  <si>
+    <t>Page loads only once; no duplicate tabs or errors are displayed</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_03</t>
+  </si>
+  <si>
+    <t>1. User is logged in.
+2. User is on the 'Post Your Property' page.</t>
+  </si>
+  <si>
+    <t>Verify selection of Residential property type, Rent ad type, and city/location allows user to proceed</t>
+  </si>
+  <si>
+    <t>1. Click on “Post Now”
+2. Select Residential under Property Type
+3. Select Rent under Ad Type
+4. Select a City/Location
+5. Click “Start Posting Your AD For Free”</t>
+  </si>
+  <si>
+    <t>Property Type: Residential
+Ad Type: Rent
+Location: Bangalore</t>
+  </si>
+  <si>
+    <t>User is navigated to the Form Page successfully</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_04</t>
+  </si>
+  <si>
+    <t>Verify city/location dropdown selection functionality</t>
+  </si>
+  <si>
+    <t>1. Click on the City/Location dropdown
+2. View the list of available cities
+3. Select a city from the dropdown (e.g., Bangalore)</t>
+  </si>
+  <si>
+    <t>Location: Bangalore</t>
+  </si>
+  <si>
+    <t>Dropdown displays list of cities and selected city is shown correctly</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_05</t>
+  </si>
+  <si>
+    <t>1. User is on the 'Post Your Property' page</t>
+  </si>
+  <si>
+    <t>Verify validation when city is not selected</t>
+  </si>
+  <si>
+    <t>1. Click on “Post Now”
+2. Select Residential under Property Type
+3. Select Rent under Ad Type
+4. Do NOT select City/Location
+5. Click “Start Posting Your AD For Free”</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Validation error is shown: 'Please select a valid city'</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_06</t>
+  </si>
+  <si>
+    <t>1. User is on the Property Details page
+2. Residential Rent type selected</t>
+  </si>
+  <si>
+    <t>Verify selection of apartment type, BHK, floor, facing, and property age</t>
+  </si>
+  <si>
+    <t>1. Select Apartment Type (e.g., Independent House/Villa)
+2. Select BHK (e.g., 2 BHK)
+3. Select Floor (e.g., 3)
+4. Select Property Age (e.g., 5-10 years)
+5. Select Facing (e.g., East)</t>
+  </si>
+  <si>
+    <t>Apartment Type: Independent House/Villa
+BHK: 2 BHK
+Floor: 3
+Property Age: 5-10 years
+Facing: East</t>
+  </si>
+  <si>
+    <t>Selected values are displayed correctly in their respective dropdown fields</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_07</t>
+  </si>
+  <si>
+    <t>1. User is on the Property Details page</t>
+  </si>
+  <si>
+    <t>Validate Property Details form with valid inputs</t>
+  </si>
+  <si>
+    <t>1. Select Apartment Type (e.g., Independent House/Villa)
+2. Select BHK (e.g., 2 BHK)
+3. Select Floor (e.g., 3)
+4. Select Property Age (e.g., 5-10 years)
+5. Select Facing (e.g., East)
+6. Enter built-up area (e.g., 1200 sq ft)
+7. Click Save &amp; Continue</t>
+  </si>
+  <si>
+    <t>Apartment Type: Independent House/Villa
+BHK: 2 BHK
+Floor: 3
+Property Age: 5-10 years
+Facing: East
+Built-up Area: 1200 sq ft</t>
+  </si>
+  <si>
+    <t>All valid inputs are accepted, no validation errors are shown, and user successfully navigates to the Locality Details.</t>
+  </si>
+  <si>
+    <t>All valid inputs are accepted, no validation errors are shown, and user successfully navigates to the Locality Details</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_08</t>
+  </si>
+  <si>
+    <t>Verify validation when mandatory fields are empty</t>
+  </si>
+  <si>
+    <t>1. Leave all mandatory fields on Property Details page empty
+2. Click Save &amp; Continue</t>
+  </si>
+  <si>
+    <t>Validation messages appear for all empty mandatory fields</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_09</t>
+  </si>
+  <si>
+    <t>Verify validation for exceeding built-up area limit</t>
+  </si>
+  <si>
+    <t>1. Enter built-up area greater than allowed limit (e.g., 49200000)
+2. Fill remaining mandatory fields
+3. Click Save &amp; Continue</t>
+  </si>
+  <si>
+    <t>Built-up Area: 49200000</t>
+  </si>
+  <si>
+    <t>Error message is displayed (e.g., Built Up Area can't be more than 99,999)</t>
+  </si>
+  <si>
+    <t>Error message is displayed: Built Up Area can't be more than 99,999</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_10</t>
+  </si>
+  <si>
+    <t>Verify validation for insufficient built-up area based on BHK</t>
+  </si>
+  <si>
+    <t>1. Select BHK (e.g., 4 BHK)
+2. Enter built-up area less than recommended (e.g., 1200 or 1400)
+3. Observe popup message</t>
+  </si>
+  <si>
+    <t>1 RK → 120
+1 BHK → 350
+2 BHK → 600
+3 BHK → 1200
+4 BHK → 1400</t>
+  </si>
+  <si>
+    <t>System shows warning popup (e.g., “area is too small for selected BHK”) with options like:
+1. I want to change it
+2. The data is correct</t>
+  </si>
+  <si>
+    <t>System shows warning popup indicating area is too small for selected BHK with options: 'I want to change it' and 'The data is correct'</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_11</t>
+  </si>
+  <si>
+    <t>1. User is on the Locality Details page</t>
+  </si>
+  <si>
+    <t>Verify city and locality dropdown selections are functional</t>
+  </si>
+  <si>
+    <t>1. Click City dropdown and select 'Mumbai'
+2. Click Locality dropdown and select a locality</t>
+  </si>
+  <si>
+    <t>City: Mumbai
+Locality: Andheri West</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_12</t>
+  </si>
+  <si>
+    <t>Validate Locality Details form with valid inputs</t>
+  </si>
+  <si>
+    <t>1. Click City dropdown and select 'Mumbai'
+2. Click Locality dropdown and select a locality
+3. Click on Landmark/Street field
+4. Enter text 'Near Metro Station'
+5. Click Save &amp; Continue</t>
+  </si>
+  <si>
+    <t>City: Mumbai
+Locality: Andheri West
+Landmark: Near Metro Station</t>
+  </si>
+  <si>
+    <t>All valid inputs are accepted, no validation errors are shown, and user successfully navigates to the Rental Details.</t>
+  </si>
+  <si>
+    <t>All valid inputs are accepted, no validation errors are shown, and user successfully navigates to the Rental Details</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_13</t>
+  </si>
+  <si>
+    <t>Verify validation when locality/location is not selected</t>
+  </si>
+  <si>
+    <t>1. Leave locality and map location fields empty
+2. Click Save &amp; Continue</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_14</t>
+  </si>
+  <si>
+    <t>Verify mismatch between city and locality selection</t>
+  </si>
+  <si>
+    <t>1. Select City as Gurgaon
+2. In Locality field, select a location from a different city (e.g., Kolkata Sweet And Restaurant)
+3. Enter text 'Near Metro Station'
+4. Click Save &amp; Continue</t>
+  </si>
+  <si>
+    <t>City: Gurgaon
+Locality: Kolkata Sweet And Restaurant
+Landmark: Near Metro Station</t>
+  </si>
+  <si>
+    <t>System should display an error or prevent proceeding, indicating mismatch between selected city and locality</t>
+  </si>
+  <si>
+    <t>System allows user to proceed to next page without any validation for city and locality mismatch</t>
+  </si>
+  <si>
+    <t>Failed</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_15</t>
+  </si>
+  <si>
+    <t>1. User is on the Rental Details page</t>
+  </si>
+  <si>
+    <t>Verify dropdown selections in Rental Details</t>
+  </si>
+  <si>
+    <t>1. Select Tenant Preference (e.g., Family)
+2. Select Furnishing (e.g., Semi-furnished)
+3. Select Parking (e.g., Car)
+4. Select Monthly Maintenance (e.g., Maintenance Included)</t>
+  </si>
+  <si>
+    <t>Tenant: Family
+Furnishing: Semi-furnished
+Parking: Car
+Maintenance: Maintenance Included</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_16</t>
+  </si>
+  <si>
+    <t>Verify property availability date selection using calendar</t>
+  </si>
+  <si>
+    <t>1. Click on the Availability Date field
+2. A calendar/date picker opens
+3. Select a future date (e.g., 01 May 2025)</t>
+  </si>
+  <si>
+    <t>Availability Date: 01 May 2025</t>
+  </si>
+  <si>
+    <t>Calendar opens on click; selected availability date is saved and displayed correctly</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_17</t>
+  </si>
+  <si>
+    <t>Validate Rental Details form with valid inputs.</t>
+  </si>
+  <si>
+    <t>1. Enter Rent (e.g., 15000)
+2. Enter Deposit (e.g., 45000)
+3. Select Tenant Preference, Furnishing, Parking
+4. Select Availability Date
+5. Enter Maintenance (e.g., Maintenance Included)
+6. Click Save &amp; Continue</t>
+  </si>
+  <si>
+    <t>Rent: 15000
+Deposit: 45000
+Tenant: Family
+Furnishing: Semi-furnished
+Parking: Car
+Maintenance: Maintenance Included
+Availability Date: 01 May 2025</t>
+  </si>
+  <si>
+    <t>All valid inputs are accepted and user successfully proceeds to the Amenities page.</t>
+  </si>
+  <si>
+    <t>All valid inputs are accepted and user successfully proceeds to the Amenities page</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_18</t>
+  </si>
+  <si>
+    <t>Verify validation when deposit is less than rent.</t>
+  </si>
+  <si>
+    <t>1. Enter Rent (e.g., 15000)
+2. Enter Deposit less than rent (e.g., 10000)
+3. Fill remaining fields with valid data
+4. Click Save &amp; Continue</t>
+  </si>
+  <si>
+    <t>Rent: 15000
+Deposit: 10000</t>
+  </si>
+  <si>
+    <t>Validation error is displayed indicating deposit should be greater than or equal to rent</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_19</t>
+  </si>
+  <si>
+    <t>1. User is on the Amenities page</t>
+  </si>
+  <si>
+    <t>Verify counter and dropdown selections</t>
+  </si>
+  <si>
+    <t>1. Set Bathroom count (e.g., 2)
+2. Set Balcony count (e.g., 2)
+3. Select Water Supply (e.g., Borewell)</t>
+  </si>
+  <si>
+    <t>Bathrooms: 2
+Balcony: 2
+Water Supply: Borewell</t>
+  </si>
+  <si>
+    <t>Selected values are displayed correctly</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_20</t>
+  </si>
+  <si>
+    <t>Verify toggle and other dropdown selections</t>
+  </si>
+  <si>
+    <t>1. Select Pet Allowed → Yes
+2. Select Gym → Yes
+3. Select Non-Veg Allowed → Yes
+4. Select Gated Security → Yes
+5. Select “Who will show the property?” (e.g., Neighbours)
+6. Select Property Condition (e.g., New Property)</t>
+  </si>
+  <si>
+    <t>All toggles: Yes</t>
+  </si>
+  <si>
+    <t>All selections are reflected correctly</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_21</t>
+  </si>
+  <si>
+    <t>Validate Amenities form with valid inputs</t>
+  </si>
+  <si>
+    <t>1. Fill all required fields (bathroom, balcony, water supply)
+2. Select preferences and dropdowns
+3. Select amenities (e.g., Lift, Swimming Pool)
+4. Click Save &amp; Continue</t>
+  </si>
+  <si>
+    <t>Bathrooms: 2
+Balcony: 2
+Water Supply: Borewell
+Select Pet Allowed → Yes
+Select Gym → Yes
+Select Non-Veg Allowed → Yes
+Select Gated Security → Yes
+Select “Who will show the property?” (e.g., Neighbours)
+Select Property Condition (e.g., New Property)</t>
+  </si>
+  <si>
+    <t>All inputs are accepted and user successfully proceeds to Gallery page</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_22</t>
+  </si>
+  <si>
+    <t>Verify validation when mandatory fields are not selected</t>
+  </si>
+  <si>
+    <t>1. Leave all mandatory amenity fields blank
+2. Click Save &amp; Continue</t>
+  </si>
+  <si>
+    <t>Validation error displayed for all required amenity fields</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_23</t>
+  </si>
+  <si>
+    <t>1. User is on the Photo Upload page
+2. Valid image files available</t>
+  </si>
+  <si>
+    <t>Verify photo upload accepts valid formats (JPG, PNG)</t>
+  </si>
+  <si>
+    <t>1. Click on Upload Photo button
+2. Select a JPG image file
+3. Verify it uploads successfully
+4. Repeat with a PNG file
+5. Click Save &amp; Continue</t>
+  </si>
+  <si>
+    <t>Image1.jpg (&lt; 5MB)
+Image2.png (&lt; 5MB)</t>
+  </si>
+  <si>
+    <t>Both JPG and PNG photos are uploaded and preview thumbnails are shown</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_24</t>
+  </si>
+  <si>
+    <t>1. User is on the Photo Upload page
+2. Valid video file available</t>
+  </si>
+  <si>
+    <t>Verify video upload accepts valid format (MP4)</t>
+  </si>
+  <si>
+    <t>1. Click on Upload Video button
+2. Select a valid MP4 video file
+3. Click Save &amp; Continue</t>
+  </si>
+  <si>
+    <t>Video.mp4 (&lt; 50MB)</t>
+  </si>
+  <si>
+    <t>MP4 video is uploaded and a preview thumbnail is shown</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_25</t>
+  </si>
+  <si>
+    <t>1. User is on the Photo Upload page</t>
+  </si>
+  <si>
+    <t>Verify uploaded media is displayed as a preview thumbnail</t>
+  </si>
+  <si>
+    <t>1. Upload a JPG image
+2. Observe the preview area after upload completes</t>
+  </si>
+  <si>
+    <t>Image1.jpg</t>
+  </si>
+  <si>
+    <t>Thumbnail preview of the uploaded image is visible in the upload section</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_26</t>
+  </si>
+  <si>
+    <t>1. User is on the Visit Schedule page</t>
+  </si>
+  <si>
+    <t>Verify availability selection (Everyday / Weekday / Weekend) along with start and end time selection</t>
+  </si>
+  <si>
+    <t>1. Select 'Everyday' availability option
+2. Set Start Time to 09:00 AM
+3. Set End Time to 06:00 PM
+4. Repeat steps 1-4 with 'Weekday' and 'Weekend'</t>
+  </si>
+  <si>
+    <t>Availability: Everyday / Weekday / Weekend
+Start: 09:00 AM
+End: 06:00 PM</t>
+  </si>
+  <si>
+    <t>Correct schedule fields appear; start and end times are set and saved correctly for each availability type</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_27</t>
+  </si>
+  <si>
+    <t>Validate Visit Schedule form with valid inputs</t>
+  </si>
+  <si>
+    <t>1. Select availability option (e.g., Everyday)
+2. Set Start Time (e.g., 09:00 AM)
+3. Set End Time (e.g., 06:00 PM)
+4. (Optional) Select “All Day” and verify behavior (if applicable skip time selection)
+5. Click Save &amp; Continue</t>
+  </si>
+  <si>
+    <t>Availability: Everyday
+Start Time: 09:00 AM
+End Time: 06:00 PM</t>
+  </si>
+  <si>
+    <t>All inputs are accepted and user successfully proceeds to the next step</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_28</t>
+  </si>
+  <si>
+    <t>Verify validation when time or availability is not selected</t>
+  </si>
+  <si>
+    <t>1. Leave availability and time fields empty
+2. Click Save &amp; Continue</t>
+  </si>
+  <si>
+    <t>Validation error displayed: 'Please select availability and visit time'</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_29</t>
+  </si>
+  <si>
+    <t>1. All property details have been entered
+2. User clicks Submit/Post</t>
+  </si>
+  <si>
+    <t>Verify success message is displayed upon property submission</t>
+  </si>
+  <si>
+    <t>1. Complete all property posting steps
+2. Click Submit/Post button
+3. Observe the confirmation screen</t>
+  </si>
+  <si>
+    <t>All valid property data entered</t>
+  </si>
+  <si>
+    <t>Success message is displayed: 'Your property has been posted successfully!'</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_30</t>
+  </si>
+  <si>
+    <t>1. Property has been submitted successfully
+2. User is on the success screen</t>
+  </si>
+  <si>
+    <t>Verify user can edit the listing from the success screen</t>
+  </si>
+  <si>
+    <t>1. On success screen, click 'Edit Listing' button
+2. Observe where user is redirected</t>
+  </si>
+  <si>
+    <t>User is navigated back to the property details form with existing data pre-filled</t>
+  </si>
+  <si>
+    <t>TC_NoBroker_31</t>
+  </si>
+  <si>
+    <t>Verify 'Preview Listing' shows all entered property details accurately</t>
+  </si>
+  <si>
+    <t>1. On success screen, click 'Preview Listing' button
+2. Review all sections in the preview</t>
+  </si>
+  <si>
+    <t>Preview shows all entered details (property type, rent, locality, amenities, photos) correctly</t>
+  </si>
+  <si>
+    <t>Defect Id.</t>
+  </si>
+  <si>
+    <t>Module name</t>
+  </si>
+  <si>
+    <t>Defect Summary</t>
+  </si>
+  <si>
+    <t>Defect Priority</t>
+  </si>
+  <si>
+    <t>Assigned To</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>DR_NoBroker_01</t>
+  </si>
+  <si>
+    <t>Post Property</t>
+  </si>
+  <si>
+    <t>System allows user to proceed with mismatched city and locality selection (e.g., Gurgaon city with Kolkata locality) without showing any validation error, leading to incorrect property location data.</t>
+  </si>
+  <si>
+    <t>New</t>
+  </si>
+  <si>
+    <t>BR_ID</t>
+  </si>
+  <si>
+    <t>TR_ID</t>
+  </si>
+  <si>
+    <t>TS_ID</t>
+  </si>
+  <si>
+    <t>TC_ID</t>
+  </si>
+  <si>
+    <t>STATUS</t>
+  </si>
+  <si>
+    <t>DR_ID</t>
+  </si>
+  <si>
+    <t>BR_NoBroker_01</t>
+  </si>
+  <si>
+    <t>TR_NoBroker_01</t>
+  </si>
+  <si>
+    <t>PASSED</t>
+  </si>
+  <si>
+    <t>BR_NoBroker_02</t>
+  </si>
+  <si>
+    <t>TR_NoBroker_02</t>
+  </si>
+  <si>
+    <t>BR_NoBroker_03</t>
+  </si>
+  <si>
+    <t>TR_NoBroker_03</t>
+  </si>
+  <si>
+    <t>BR_NoBroker_04</t>
+  </si>
+  <si>
+    <t>TR_NoBroker_04</t>
+  </si>
+  <si>
+    <t>FAILED</t>
+  </si>
+  <si>
+    <t>BR_NoBroker_05</t>
+  </si>
+  <si>
+    <t>TR_NoBroker_05</t>
+  </si>
+  <si>
+    <t>BR_NoBroker_06</t>
+  </si>
+  <si>
+    <t>TR_NoBroker_06</t>
+  </si>
+  <si>
+    <t>BR_NoBroker_07</t>
+  </si>
+  <si>
+    <t>TR_NoBroker_07</t>
+  </si>
+  <si>
+    <t>BR_NoBroker_08</t>
+  </si>
+  <si>
+    <t>TR_NoBroker_08</t>
+  </si>
+  <si>
+    <t>BR_NoBroker_09</t>
+  </si>
+  <si>
+    <t>TR_NoBroker_09</t>
+  </si>
+  <si>
+    <t>TEST EXECUTION SUMMARY</t>
+  </si>
+  <si>
+    <t>Project Name</t>
+  </si>
+  <si>
+    <t>Module Name</t>
+  </si>
+  <si>
+    <t>Total Cases</t>
+  </si>
+  <si>
+    <t>Total Passed</t>
+  </si>
+  <si>
+    <t>Total Failed</t>
+  </si>
+  <si>
+    <t>Total Executed</t>
+  </si>
+  <si>
+    <t>Pass Percentage</t>
+  </si>
+  <si>
+    <t>Fail Percentage</t>
+  </si>
+  <si>
+    <t>Complition Percentage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NoBroker
+</t>
+  </si>
+  <si>
+    <t>Post Your Property – Navigate to Post Your Property Page</t>
+  </si>
+  <si>
+    <t>Post Your Property – Select Property Type and Ad Type</t>
+  </si>
+  <si>
+    <t>Post Your Property – Enter Property Details</t>
+  </si>
+  <si>
+    <t>Post Your Property – Enter Locality Details</t>
+  </si>
+  <si>
+    <t>Post Your Property – Enter Rental Details</t>
+  </si>
+  <si>
+    <t>Post Your Property – Enter Amenities and Additional Details</t>
+  </si>
+  <si>
+    <t>Post Your Property – Upload Property Photos and Videos</t>
+  </si>
+  <si>
+    <t>Post Your Property – Set Property Visit Schedule</t>
+  </si>
+  <si>
+    <t>Post Your Property – Verify Property Posting Success</t>
+  </si>
+  <si>
+    <t>Overall</t>
+  </si>
+  <si>
+    <t>Post Your Property</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -446,13 +1293,72 @@
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF276221"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="31">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -521,12 +1427,120 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF1A983"/>
+        <fgColor rgb="FF7B3F2A"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFD966"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4B084"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC43131"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCAEDFB"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBF1DE"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -588,29 +1602,222 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFD9D9D9"/>
+        <color indexed="64"/>
       </left>
       <right style="thin">
-        <color rgb="FFD9D9D9"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color rgb="FFD9D9D9"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFD9D9D9"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right style="thin">
-        <color rgb="FFD9D9D9"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color rgb="FFD9D9D9"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFD9D9D9"/>
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -618,7 +1825,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="121">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -630,9 +1837,6 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -660,14 +1864,275 @@
     <xf numFmtId="0" fontId="8" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="25" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="13" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="29" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="18" fillId="27" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="26" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="26" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="27" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="27" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="27" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="26" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="26" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFC43131"/>
+      <color rgb="FFC41B1B"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1438,208 +2903,208 @@
     <col min="2" max="2" width="22.5703125" customWidth="1"/>
     <col min="3" max="3" width="32.85546875" customWidth="1"/>
     <col min="4" max="4" width="31.7109375" customWidth="1"/>
-    <col min="5" max="5" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="24.7109375" customWidth="1"/>
     <col min="6" max="6" width="49" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="48">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:6" ht="24">
+      <c r="A1" s="120" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="120" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="120" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="120" t="s">
         <v>62</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="120" t="s">
         <v>63</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="120" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="238.5">
-      <c r="A2" s="12" t="s">
+    <row r="2" spans="1:6" ht="58.5" customHeight="1">
+      <c r="A2" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="C2" s="13" t="s">
-        <v>7</v>
+      <c r="C2" s="12" t="s">
+        <v>67</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="E2" s="14">
+        <v>68</v>
+      </c>
+      <c r="E2" s="13">
+        <v>2</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="145.5" customHeight="1">
+      <c r="A3" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="E3" s="16">
         <v>3</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="F3" s="15" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="139.5" customHeight="1">
+      <c r="A4" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="D4" s="19" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="309.75">
-      <c r="A3" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="B3" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="C3" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="E3" s="17">
+      <c r="E4" s="19">
+        <v>5</v>
+      </c>
+      <c r="F4" s="18" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="201" customHeight="1">
+      <c r="A5" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="E5" s="19">
         <v>4</v>
       </c>
-      <c r="F3" s="16" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="321.75">
-      <c r="A4" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="B4" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="C4" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="19" t="s">
-        <v>67</v>
-      </c>
-      <c r="E4" s="20">
+      <c r="F5" s="18" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="116.25" customHeight="1">
+      <c r="A6" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="E6" s="16">
         <v>4</v>
       </c>
-      <c r="F4" s="19" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="345.75">
-      <c r="A5" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="B5" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="19" t="s">
-        <v>67</v>
-      </c>
-      <c r="E5" s="20">
+      <c r="F6" s="15" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="107.25" customHeight="1">
+      <c r="A7" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="E7" s="19">
         <v>4</v>
       </c>
-      <c r="F5" s="19" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="357">
-      <c r="A6" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="B6" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="C6" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="E6" s="17">
-        <v>4</v>
-      </c>
-      <c r="F6" s="16" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="321.75">
-      <c r="A7" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="B7" s="19" t="s">
-        <v>82</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="D7" s="19" t="s">
-        <v>67</v>
-      </c>
-      <c r="E7" s="20">
-        <v>4</v>
-      </c>
-      <c r="F7" s="19" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="274.5">
-      <c r="A8" s="15" t="s">
-        <v>85</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>44</v>
+      <c r="F7" s="18" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="217.5" customHeight="1">
+      <c r="A8" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>92</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="E8" s="17">
+        <v>68</v>
+      </c>
+      <c r="E8" s="16">
         <v>3</v>
       </c>
-      <c r="F8" s="16" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="321.75">
-      <c r="A9" s="18" t="s">
-        <v>88</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>89</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>48</v>
+      <c r="F8" s="15" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="118.5" customHeight="1">
+      <c r="A9" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>96</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>67</v>
-      </c>
-      <c r="E9" s="20">
-        <v>4</v>
-      </c>
-      <c r="F9" s="19" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="393">
-      <c r="A10" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="B10" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="C10" s="16" t="s">
-        <v>93</v>
+        <v>68</v>
+      </c>
+      <c r="E9" s="19">
+        <v>3</v>
+      </c>
+      <c r="F9" s="18" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="145.5" customHeight="1">
+      <c r="A10" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>100</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="E10" s="17">
-        <v>4</v>
-      </c>
-      <c r="F10" s="16" t="s">
-        <v>94</v>
+        <v>68</v>
+      </c>
+      <c r="E10" s="16">
+        <v>3</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -1649,16 +3114,16 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9617B7E-8126-4222-8E15-81ED0B51EF44}">
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.140625" customWidth="1"/>
     <col min="2" max="2" width="17.140625" customWidth="1"/>
-    <col min="3" max="3" width="19.140625" customWidth="1"/>
-    <col min="4" max="4" width="25.85546875" customWidth="1"/>
-    <col min="5" max="5" width="19" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="15.28515625" customWidth="1"/>
+    <col min="3" max="3" width="34.85546875" customWidth="1"/>
+    <col min="4" max="4" width="34.7109375" customWidth="1"/>
+    <col min="5" max="5" width="54.5703125" customWidth="1"/>
+    <col min="6" max="6" width="35.140625" customWidth="1"/>
+    <col min="7" max="7" width="30" customWidth="1"/>
     <col min="8" max="8" width="29.140625" customWidth="1"/>
     <col min="9" max="9" width="17.5703125" customWidth="1"/>
     <col min="10" max="10" width="29.42578125" customWidth="1"/>
@@ -1667,48 +3132,2177 @@
     <col min="13" max="13" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="21" t="s">
+    <row r="1" spans="1:13" ht="47.25">
+      <c r="A1" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="C1" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="D1" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="F1" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="G1" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="H1" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="I1" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="J1" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="K1" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="L1" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="M1" s="91" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" s="25" customFormat="1" ht="108" customHeight="1">
+      <c r="A2" s="22" t="s">
+        <v>115</v>
+      </c>
+      <c r="B2" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2" s="23" t="s">
+        <v>116</v>
+      </c>
+      <c r="D2" s="23" t="s">
+        <v>117</v>
+      </c>
+      <c r="E2" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="F2" s="23" t="s">
+        <v>119</v>
+      </c>
+      <c r="G2" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="H2" s="49" t="s">
+        <v>121</v>
+      </c>
+      <c r="I2" s="57" t="s">
+        <v>122</v>
+      </c>
+      <c r="J2" s="24" t="s">
+        <v>123</v>
+      </c>
+      <c r="K2" s="24" t="s">
+        <v>123</v>
+      </c>
+      <c r="L2" s="90" t="s">
+        <v>123</v>
+      </c>
+      <c r="M2" s="102" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" s="25" customFormat="1" ht="120.75" customHeight="1">
+      <c r="A3" s="26" t="s">
+        <v>124</v>
+      </c>
+      <c r="B3" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="C3" s="24" t="s">
+        <v>116</v>
+      </c>
+      <c r="D3" s="24" t="s">
+        <v>125</v>
+      </c>
+      <c r="E3" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="F3" s="24" t="s">
+        <v>127</v>
+      </c>
+      <c r="G3" s="24" t="s">
+        <v>128</v>
+      </c>
+      <c r="H3" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="I3" s="58" t="s">
+        <v>122</v>
+      </c>
+      <c r="J3" s="24" t="s">
+        <v>123</v>
+      </c>
+      <c r="K3" s="24" t="s">
+        <v>123</v>
+      </c>
+      <c r="L3" s="90" t="s">
+        <v>123</v>
+      </c>
+      <c r="M3" s="102" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" s="29" customFormat="1" ht="98.25" customHeight="1">
+      <c r="A4" s="27" t="s">
+        <v>129</v>
+      </c>
+      <c r="B4" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="D4" s="28" t="s">
+        <v>131</v>
+      </c>
+      <c r="E4" s="28" t="s">
+        <v>132</v>
+      </c>
+      <c r="F4" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="G4" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="H4" s="51" t="s">
+        <v>134</v>
+      </c>
+      <c r="I4" s="58" t="s">
+        <v>122</v>
+      </c>
+      <c r="J4" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="K4" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="L4" s="92" t="s">
+        <v>123</v>
+      </c>
+      <c r="M4" s="103" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" s="29" customFormat="1" ht="75" customHeight="1">
+      <c r="A5" s="27" t="s">
+        <v>135</v>
+      </c>
+      <c r="B5" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="D5" s="28" t="s">
+        <v>136</v>
+      </c>
+      <c r="E5" s="28" t="s">
+        <v>137</v>
+      </c>
+      <c r="F5" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="G5" s="28" t="s">
+        <v>139</v>
+      </c>
+      <c r="H5" s="51" t="s">
+        <v>139</v>
+      </c>
+      <c r="I5" s="58" t="s">
+        <v>122</v>
+      </c>
+      <c r="J5" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="K5" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="L5" s="92" t="s">
+        <v>123</v>
+      </c>
+      <c r="M5" s="104" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" s="29" customFormat="1" ht="99.75" customHeight="1">
+      <c r="A6" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="B6" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6" s="28" t="s">
+        <v>141</v>
+      </c>
+      <c r="D6" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="E6" s="28" t="s">
+        <v>143</v>
+      </c>
+      <c r="F6" s="28" t="s">
+        <v>144</v>
+      </c>
+      <c r="G6" s="28" t="s">
+        <v>145</v>
+      </c>
+      <c r="H6" s="51" t="s">
+        <v>145</v>
+      </c>
+      <c r="I6" s="58" t="s">
+        <v>122</v>
+      </c>
+      <c r="J6" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="K6" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="L6" s="92" t="s">
+        <v>123</v>
+      </c>
+      <c r="M6" s="105" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" s="32" customFormat="1" ht="89.25" customHeight="1">
+      <c r="A7" s="30" t="s">
+        <v>146</v>
+      </c>
+      <c r="B7" s="31" t="s">
+        <v>74</v>
+      </c>
+      <c r="C7" s="31" t="s">
+        <v>147</v>
+      </c>
+      <c r="D7" s="31" t="s">
+        <v>148</v>
+      </c>
+      <c r="E7" s="31" t="s">
+        <v>149</v>
+      </c>
+      <c r="F7" s="31" t="s">
+        <v>150</v>
+      </c>
+      <c r="G7" s="31" t="s">
+        <v>151</v>
+      </c>
+      <c r="H7" s="52" t="s">
+        <v>151</v>
+      </c>
+      <c r="I7" s="58" t="s">
+        <v>122</v>
+      </c>
+      <c r="J7" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="K7" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="L7" s="93" t="s">
+        <v>123</v>
+      </c>
+      <c r="M7" s="106" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" s="32" customFormat="1" ht="87.75" customHeight="1">
+      <c r="A8" s="30" t="s">
+        <v>152</v>
+      </c>
+      <c r="B8" s="31" t="s">
+        <v>74</v>
+      </c>
+      <c r="C8" s="31" t="s">
+        <v>153</v>
+      </c>
+      <c r="D8" s="31" t="s">
+        <v>154</v>
+      </c>
+      <c r="E8" s="31" t="s">
+        <v>155</v>
+      </c>
+      <c r="F8" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="G8" s="31" t="s">
+        <v>157</v>
+      </c>
+      <c r="H8" s="52" t="s">
+        <v>158</v>
+      </c>
+      <c r="I8" s="58" t="s">
+        <v>122</v>
+      </c>
+      <c r="J8" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="K8" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="L8" s="93" t="s">
+        <v>123</v>
+      </c>
+      <c r="M8" s="106" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" s="32" customFormat="1" ht="69" customHeight="1">
+      <c r="A9" s="30" t="s">
+        <v>159</v>
+      </c>
+      <c r="B9" s="31" t="s">
+        <v>74</v>
+      </c>
+      <c r="C9" s="31" t="s">
+        <v>153</v>
+      </c>
+      <c r="D9" s="31" t="s">
+        <v>160</v>
+      </c>
+      <c r="E9" s="31" t="s">
+        <v>161</v>
+      </c>
+      <c r="F9" s="31" t="s">
+        <v>144</v>
+      </c>
+      <c r="G9" s="31" t="s">
+        <v>162</v>
+      </c>
+      <c r="H9" s="52" t="s">
+        <v>162</v>
+      </c>
+      <c r="I9" s="58" t="s">
+        <v>122</v>
+      </c>
+      <c r="J9" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="K9" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="L9" s="93" t="s">
+        <v>123</v>
+      </c>
+      <c r="M9" s="106" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" s="32" customFormat="1" ht="66" customHeight="1">
+      <c r="A10" s="30" t="s">
+        <v>163</v>
+      </c>
+      <c r="B10" s="31" t="s">
+        <v>74</v>
+      </c>
+      <c r="C10" s="31" t="s">
+        <v>153</v>
+      </c>
+      <c r="D10" s="31" t="s">
+        <v>164</v>
+      </c>
+      <c r="E10" s="31" t="s">
+        <v>165</v>
+      </c>
+      <c r="F10" s="31" t="s">
+        <v>166</v>
+      </c>
+      <c r="G10" s="31" t="s">
+        <v>167</v>
+      </c>
+      <c r="H10" s="52" t="s">
+        <v>168</v>
+      </c>
+      <c r="I10" s="58" t="s">
+        <v>122</v>
+      </c>
+      <c r="J10" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="K10" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="L10" s="93" t="s">
+        <v>123</v>
+      </c>
+      <c r="M10" s="106" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" s="32" customFormat="1" ht="66" customHeight="1">
+      <c r="A11" s="30" t="s">
+        <v>169</v>
+      </c>
+      <c r="B11" s="31" t="s">
+        <v>74</v>
+      </c>
+      <c r="C11" s="31" t="s">
+        <v>153</v>
+      </c>
+      <c r="D11" s="31" t="s">
+        <v>170</v>
+      </c>
+      <c r="E11" s="31" t="s">
+        <v>171</v>
+      </c>
+      <c r="F11" s="31" t="s">
+        <v>172</v>
+      </c>
+      <c r="G11" s="31" t="s">
+        <v>173</v>
+      </c>
+      <c r="H11" s="52" t="s">
+        <v>174</v>
+      </c>
+      <c r="I11" s="58" t="s">
+        <v>122</v>
+      </c>
+      <c r="J11" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="K11" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="L11" s="93" t="s">
+        <v>123</v>
+      </c>
+      <c r="M11" s="106" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" s="35" customFormat="1" ht="92.25" customHeight="1">
+      <c r="A12" s="33" t="s">
+        <v>175</v>
+      </c>
+      <c r="B12" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="C12" s="34" t="s">
+        <v>176</v>
+      </c>
+      <c r="D12" s="34" t="s">
+        <v>177</v>
+      </c>
+      <c r="E12" s="34" t="s">
+        <v>178</v>
+      </c>
+      <c r="F12" s="34" t="s">
+        <v>179</v>
+      </c>
+      <c r="G12" s="34" t="s">
+        <v>151</v>
+      </c>
+      <c r="H12" s="53" t="s">
+        <v>151</v>
+      </c>
+      <c r="I12" s="58" t="s">
+        <v>122</v>
+      </c>
+      <c r="J12" s="34" t="s">
+        <v>123</v>
+      </c>
+      <c r="K12" s="34" t="s">
+        <v>123</v>
+      </c>
+      <c r="L12" s="94" t="s">
+        <v>123</v>
+      </c>
+      <c r="M12" s="107" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" s="35" customFormat="1" ht="95.25" customHeight="1">
+      <c r="A13" s="33" t="s">
+        <v>180</v>
+      </c>
+      <c r="B13" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" s="34" t="s">
+        <v>176</v>
+      </c>
+      <c r="D13" s="34" t="s">
+        <v>181</v>
+      </c>
+      <c r="E13" s="34" t="s">
+        <v>182</v>
+      </c>
+      <c r="F13" s="34" t="s">
+        <v>183</v>
+      </c>
+      <c r="G13" s="34" t="s">
+        <v>184</v>
+      </c>
+      <c r="H13" s="53" t="s">
+        <v>185</v>
+      </c>
+      <c r="I13" s="58" t="s">
+        <v>122</v>
+      </c>
+      <c r="J13" s="34" t="s">
+        <v>123</v>
+      </c>
+      <c r="K13" s="34" t="s">
+        <v>123</v>
+      </c>
+      <c r="L13" s="94" t="s">
+        <v>123</v>
+      </c>
+      <c r="M13" s="107" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" s="35" customFormat="1" ht="95.25" customHeight="1">
+      <c r="A14" s="33" t="s">
+        <v>186</v>
+      </c>
+      <c r="B14" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="C14" s="34" t="s">
+        <v>176</v>
+      </c>
+      <c r="D14" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="E14" s="34" t="s">
+        <v>188</v>
+      </c>
+      <c r="F14" s="34" t="s">
+        <v>144</v>
+      </c>
+      <c r="G14" s="34" t="s">
+        <v>162</v>
+      </c>
+      <c r="H14" s="53" t="s">
+        <v>162</v>
+      </c>
+      <c r="I14" s="58" t="s">
+        <v>122</v>
+      </c>
+      <c r="J14" s="34" t="s">
+        <v>123</v>
+      </c>
+      <c r="K14" s="34" t="s">
+        <v>123</v>
+      </c>
+      <c r="L14" s="94" t="s">
+        <v>123</v>
+      </c>
+      <c r="M14" s="107" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" s="35" customFormat="1" ht="95.25" customHeight="1">
+      <c r="A15" s="33" t="s">
+        <v>189</v>
+      </c>
+      <c r="B15" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="C15" s="34" t="s">
+        <v>176</v>
+      </c>
+      <c r="D15" s="34" t="s">
+        <v>190</v>
+      </c>
+      <c r="E15" s="34" t="s">
+        <v>191</v>
+      </c>
+      <c r="F15" s="34" t="s">
+        <v>192</v>
+      </c>
+      <c r="G15" s="34" t="s">
+        <v>193</v>
+      </c>
+      <c r="H15" s="53" t="s">
+        <v>194</v>
+      </c>
+      <c r="I15" s="59" t="s">
+        <v>195</v>
+      </c>
+      <c r="J15" s="34" t="s">
+        <v>123</v>
+      </c>
+      <c r="K15" s="34" t="s">
+        <v>123</v>
+      </c>
+      <c r="L15" s="94" t="s">
+        <v>123</v>
+      </c>
+      <c r="M15" s="107" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" s="38" customFormat="1" ht="69" customHeight="1">
+      <c r="A16" s="36" t="s">
+        <v>196</v>
+      </c>
+      <c r="B16" s="37" t="s">
+        <v>82</v>
+      </c>
+      <c r="C16" s="37" t="s">
+        <v>197</v>
+      </c>
+      <c r="D16" s="37" t="s">
+        <v>198</v>
+      </c>
+      <c r="E16" s="37" t="s">
+        <v>199</v>
+      </c>
+      <c r="F16" s="37" t="s">
+        <v>200</v>
+      </c>
+      <c r="G16" s="37" t="s">
+        <v>151</v>
+      </c>
+      <c r="H16" s="54" t="s">
+        <v>151</v>
+      </c>
+      <c r="I16" s="58" t="s">
+        <v>122</v>
+      </c>
+      <c r="J16" s="37" t="s">
+        <v>123</v>
+      </c>
+      <c r="K16" s="37" t="s">
+        <v>123</v>
+      </c>
+      <c r="L16" s="95" t="s">
+        <v>123</v>
+      </c>
+      <c r="M16" s="108" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" s="38" customFormat="1" ht="36">
+      <c r="A17" s="36" t="s">
+        <v>201</v>
+      </c>
+      <c r="B17" s="37" t="s">
+        <v>82</v>
+      </c>
+      <c r="C17" s="37" t="s">
+        <v>197</v>
+      </c>
+      <c r="D17" s="37" t="s">
+        <v>202</v>
+      </c>
+      <c r="E17" s="37" t="s">
+        <v>203</v>
+      </c>
+      <c r="F17" s="37" t="s">
+        <v>204</v>
+      </c>
+      <c r="G17" s="37" t="s">
+        <v>205</v>
+      </c>
+      <c r="H17" s="54" t="s">
+        <v>205</v>
+      </c>
+      <c r="I17" s="58" t="s">
+        <v>122</v>
+      </c>
+      <c r="J17" s="37" t="s">
+        <v>123</v>
+      </c>
+      <c r="K17" s="37" t="s">
+        <v>123</v>
+      </c>
+      <c r="L17" s="95" t="s">
+        <v>123</v>
+      </c>
+      <c r="M17" s="108" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" s="38" customFormat="1" ht="84">
+      <c r="A18" s="36" t="s">
+        <v>206</v>
+      </c>
+      <c r="B18" s="37" t="s">
+        <v>82</v>
+      </c>
+      <c r="C18" s="37" t="s">
+        <v>197</v>
+      </c>
+      <c r="D18" s="37" t="s">
+        <v>207</v>
+      </c>
+      <c r="E18" s="37" t="s">
+        <v>208</v>
+      </c>
+      <c r="F18" s="37" t="s">
+        <v>209</v>
+      </c>
+      <c r="G18" s="37" t="s">
+        <v>210</v>
+      </c>
+      <c r="H18" s="54" t="s">
+        <v>211</v>
+      </c>
+      <c r="I18" s="58" t="s">
+        <v>122</v>
+      </c>
+      <c r="J18" s="37" t="s">
+        <v>123</v>
+      </c>
+      <c r="K18" s="37" t="s">
+        <v>123</v>
+      </c>
+      <c r="L18" s="95" t="s">
+        <v>123</v>
+      </c>
+      <c r="M18" s="108" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" s="38" customFormat="1" ht="48">
+      <c r="A19" s="36" t="s">
+        <v>212</v>
+      </c>
+      <c r="B19" s="37" t="s">
+        <v>82</v>
+      </c>
+      <c r="C19" s="37" t="s">
+        <v>197</v>
+      </c>
+      <c r="D19" s="37" t="s">
+        <v>213</v>
+      </c>
+      <c r="E19" s="37" t="s">
+        <v>214</v>
+      </c>
+      <c r="F19" s="37" t="s">
+        <v>215</v>
+      </c>
+      <c r="G19" s="37" t="s">
+        <v>216</v>
+      </c>
+      <c r="H19" s="54" t="s">
+        <v>216</v>
+      </c>
+      <c r="I19" s="58" t="s">
+        <v>122</v>
+      </c>
+      <c r="J19" s="37" t="s">
+        <v>123</v>
+      </c>
+      <c r="K19" s="37" t="s">
+        <v>123</v>
+      </c>
+      <c r="L19" s="95" t="s">
+        <v>123</v>
+      </c>
+      <c r="M19" s="109" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" s="41" customFormat="1" ht="118.5" customHeight="1">
+      <c r="A20" s="39" t="s">
+        <v>217</v>
+      </c>
+      <c r="B20" s="40" t="s">
+        <v>86</v>
+      </c>
+      <c r="C20" s="40" t="s">
+        <v>218</v>
+      </c>
+      <c r="D20" s="40" t="s">
+        <v>219</v>
+      </c>
+      <c r="E20" s="40" t="s">
+        <v>220</v>
+      </c>
+      <c r="F20" s="40" t="s">
+        <v>221</v>
+      </c>
+      <c r="G20" s="40" t="s">
+        <v>222</v>
+      </c>
+      <c r="H20" s="55" t="s">
+        <v>222</v>
+      </c>
+      <c r="I20" s="58" t="s">
+        <v>122</v>
+      </c>
+      <c r="J20" s="40" t="s">
+        <v>123</v>
+      </c>
+      <c r="K20" s="40" t="s">
+        <v>123</v>
+      </c>
+      <c r="L20" s="101" t="s">
+        <v>123</v>
+      </c>
+      <c r="M20" s="110" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" s="41" customFormat="1" ht="171" customHeight="1">
+      <c r="A21" s="39" t="s">
+        <v>223</v>
+      </c>
+      <c r="B21" s="40" t="s">
+        <v>86</v>
+      </c>
+      <c r="C21" s="40" t="s">
+        <v>218</v>
+      </c>
+      <c r="D21" s="40" t="s">
+        <v>224</v>
+      </c>
+      <c r="E21" s="40" t="s">
+        <v>225</v>
+      </c>
+      <c r="F21" s="40" t="s">
+        <v>226</v>
+      </c>
+      <c r="G21" s="40" t="s">
+        <v>227</v>
+      </c>
+      <c r="H21" s="55" t="s">
+        <v>227</v>
+      </c>
+      <c r="I21" s="58" t="s">
+        <v>122</v>
+      </c>
+      <c r="J21" s="40" t="s">
+        <v>123</v>
+      </c>
+      <c r="K21" s="40" t="s">
+        <v>123</v>
+      </c>
+      <c r="L21" s="101" t="s">
+        <v>123</v>
+      </c>
+      <c r="M21" s="110" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" s="41" customFormat="1" ht="130.5">
+      <c r="A22" s="39" t="s">
+        <v>228</v>
+      </c>
+      <c r="B22" s="40" t="s">
+        <v>86</v>
+      </c>
+      <c r="C22" s="40" t="s">
+        <v>218</v>
+      </c>
+      <c r="D22" s="40" t="s">
+        <v>229</v>
+      </c>
+      <c r="E22" s="40" t="s">
+        <v>230</v>
+      </c>
+      <c r="F22" s="40" t="s">
+        <v>231</v>
+      </c>
+      <c r="G22" s="40" t="s">
+        <v>232</v>
+      </c>
+      <c r="H22" s="55" t="s">
+        <v>232</v>
+      </c>
+      <c r="I22" s="58" t="s">
+        <v>122</v>
+      </c>
+      <c r="J22" s="40" t="s">
+        <v>123</v>
+      </c>
+      <c r="K22" s="40" t="s">
+        <v>123</v>
+      </c>
+      <c r="L22" s="101" t="s">
+        <v>123</v>
+      </c>
+      <c r="M22" s="110" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" s="41" customFormat="1" ht="24">
+      <c r="A23" s="39" t="s">
+        <v>233</v>
+      </c>
+      <c r="B23" s="40" t="s">
+        <v>86</v>
+      </c>
+      <c r="C23" s="40" t="s">
+        <v>218</v>
+      </c>
+      <c r="D23" s="40" t="s">
+        <v>234</v>
+      </c>
+      <c r="E23" s="40" t="s">
+        <v>235</v>
+      </c>
+      <c r="F23" s="40" t="s">
+        <v>144</v>
+      </c>
+      <c r="G23" s="40" t="s">
+        <v>236</v>
+      </c>
+      <c r="H23" s="55" t="s">
+        <v>236</v>
+      </c>
+      <c r="I23" s="58" t="s">
+        <v>122</v>
+      </c>
+      <c r="J23" s="40" t="s">
+        <v>123</v>
+      </c>
+      <c r="K23" s="40" t="s">
+        <v>123</v>
+      </c>
+      <c r="L23" s="101" t="s">
+        <v>123</v>
+      </c>
+      <c r="M23" s="110" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" s="25" customFormat="1" ht="60">
+      <c r="A24" s="26" t="s">
+        <v>237</v>
+      </c>
+      <c r="B24" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="C24" s="24" t="s">
+        <v>238</v>
+      </c>
+      <c r="D24" s="24" t="s">
+        <v>239</v>
+      </c>
+      <c r="E24" s="24" t="s">
+        <v>240</v>
+      </c>
+      <c r="F24" s="24" t="s">
+        <v>241</v>
+      </c>
+      <c r="G24" s="24" t="s">
+        <v>242</v>
+      </c>
+      <c r="H24" s="50" t="s">
+        <v>242</v>
+      </c>
+      <c r="I24" s="58" t="s">
+        <v>122</v>
+      </c>
+      <c r="J24" s="24" t="s">
+        <v>123</v>
+      </c>
+      <c r="K24" s="24" t="s">
+        <v>123</v>
+      </c>
+      <c r="L24" s="90" t="s">
+        <v>123</v>
+      </c>
+      <c r="M24" s="111" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" s="25" customFormat="1" ht="36">
+      <c r="A25" s="26" t="s">
+        <v>243</v>
+      </c>
+      <c r="B25" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="C25" s="24" t="s">
+        <v>244</v>
+      </c>
+      <c r="D25" s="24" t="s">
+        <v>245</v>
+      </c>
+      <c r="E25" s="24" t="s">
+        <v>246</v>
+      </c>
+      <c r="F25" s="24" t="s">
+        <v>247</v>
+      </c>
+      <c r="G25" s="24" t="s">
+        <v>248</v>
+      </c>
+      <c r="H25" s="50" t="s">
+        <v>248</v>
+      </c>
+      <c r="I25" s="58" t="s">
+        <v>122</v>
+      </c>
+      <c r="J25" s="24" t="s">
+        <v>123</v>
+      </c>
+      <c r="K25" s="24" t="s">
+        <v>123</v>
+      </c>
+      <c r="L25" s="90" t="s">
+        <v>123</v>
+      </c>
+      <c r="M25" s="112" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" s="25" customFormat="1" ht="103.5" customHeight="1">
+      <c r="A26" s="26" t="s">
+        <v>249</v>
+      </c>
+      <c r="B26" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="C26" s="24" t="s">
+        <v>250</v>
+      </c>
+      <c r="D26" s="24" t="s">
+        <v>251</v>
+      </c>
+      <c r="E26" s="24" t="s">
+        <v>252</v>
+      </c>
+      <c r="F26" s="24" t="s">
+        <v>253</v>
+      </c>
+      <c r="G26" s="24" t="s">
+        <v>254</v>
+      </c>
+      <c r="H26" s="50" t="s">
+        <v>254</v>
+      </c>
+      <c r="I26" s="58" t="s">
+        <v>122</v>
+      </c>
+      <c r="J26" s="24" t="s">
+        <v>123</v>
+      </c>
+      <c r="K26" s="24" t="s">
+        <v>123</v>
+      </c>
+      <c r="L26" s="90" t="s">
+        <v>123</v>
+      </c>
+      <c r="M26" s="113" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" s="32" customFormat="1" ht="48">
+      <c r="A27" s="30" t="s">
+        <v>255</v>
+      </c>
+      <c r="B27" s="31" t="s">
+        <v>94</v>
+      </c>
+      <c r="C27" s="31" t="s">
+        <v>256</v>
+      </c>
+      <c r="D27" s="31" t="s">
+        <v>257</v>
+      </c>
+      <c r="E27" s="31" t="s">
+        <v>258</v>
+      </c>
+      <c r="F27" s="31" t="s">
+        <v>259</v>
+      </c>
+      <c r="G27" s="31" t="s">
+        <v>260</v>
+      </c>
+      <c r="H27" s="52" t="s">
+        <v>260</v>
+      </c>
+      <c r="I27" s="58" t="s">
+        <v>122</v>
+      </c>
+      <c r="J27" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="K27" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="L27" s="93" t="s">
+        <v>123</v>
+      </c>
+      <c r="M27" s="114" t="s">
         <v>95</v>
       </c>
-      <c r="B1" s="22" t="s">
-        <v>96</v>
-      </c>
-      <c r="C1" s="22" t="s">
-        <v>97</v>
-      </c>
-      <c r="D1" s="22" t="s">
+    </row>
+    <row r="28" spans="1:13" s="32" customFormat="1" ht="89.25" customHeight="1">
+      <c r="A28" s="30" t="s">
+        <v>261</v>
+      </c>
+      <c r="B28" s="31" t="s">
+        <v>94</v>
+      </c>
+      <c r="C28" s="31" t="s">
+        <v>256</v>
+      </c>
+      <c r="D28" s="31" t="s">
+        <v>262</v>
+      </c>
+      <c r="E28" s="31" t="s">
+        <v>263</v>
+      </c>
+      <c r="F28" s="98" t="s">
+        <v>264</v>
+      </c>
+      <c r="G28" s="98" t="s">
+        <v>265</v>
+      </c>
+      <c r="H28" s="52" t="s">
+        <v>265</v>
+      </c>
+      <c r="I28" s="58" t="s">
+        <v>122</v>
+      </c>
+      <c r="J28" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="K28" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="L28" s="93" t="s">
+        <v>123</v>
+      </c>
+      <c r="M28" s="114" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" s="32" customFormat="1" ht="87" customHeight="1">
+      <c r="A29" s="30" t="s">
+        <v>266</v>
+      </c>
+      <c r="B29" s="31" t="s">
+        <v>94</v>
+      </c>
+      <c r="C29" s="31" t="s">
+        <v>256</v>
+      </c>
+      <c r="D29" s="31" t="s">
+        <v>267</v>
+      </c>
+      <c r="E29" s="93" t="s">
+        <v>268</v>
+      </c>
+      <c r="F29" s="99" t="s">
+        <v>144</v>
+      </c>
+      <c r="G29" s="97" t="s">
+        <v>269</v>
+      </c>
+      <c r="H29" s="100" t="s">
+        <v>269</v>
+      </c>
+      <c r="I29" s="58" t="s">
+        <v>122</v>
+      </c>
+      <c r="J29" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="K29" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="L29" s="93" t="s">
+        <v>123</v>
+      </c>
+      <c r="M29" s="114" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" s="44" customFormat="1" ht="36">
+      <c r="A30" s="42" t="s">
+        <v>270</v>
+      </c>
+      <c r="B30" s="43" t="s">
         <v>98</v>
       </c>
-      <c r="E1" s="22" t="s">
+      <c r="C30" s="43" t="s">
+        <v>271</v>
+      </c>
+      <c r="D30" s="43" t="s">
+        <v>272</v>
+      </c>
+      <c r="E30" s="43" t="s">
+        <v>273</v>
+      </c>
+      <c r="F30" s="43" t="s">
+        <v>274</v>
+      </c>
+      <c r="G30" s="43" t="s">
+        <v>275</v>
+      </c>
+      <c r="H30" s="56" t="s">
+        <v>275</v>
+      </c>
+      <c r="I30" s="58" t="s">
+        <v>122</v>
+      </c>
+      <c r="J30" s="43" t="s">
+        <v>123</v>
+      </c>
+      <c r="K30" s="43" t="s">
+        <v>123</v>
+      </c>
+      <c r="L30" s="96" t="s">
+        <v>123</v>
+      </c>
+      <c r="M30" s="115" t="s">
         <v>99</v>
       </c>
-      <c r="F1" s="22" t="s">
-        <v>100</v>
-      </c>
-      <c r="G1" s="22" t="s">
-        <v>101</v>
-      </c>
-      <c r="H1" s="22" t="s">
-        <v>102</v>
-      </c>
-      <c r="I1" s="22" t="s">
-        <v>103</v>
-      </c>
-      <c r="J1" s="22" t="s">
-        <v>104</v>
-      </c>
-      <c r="K1" s="22" t="s">
-        <v>105</v>
-      </c>
-      <c r="L1" s="22" t="s">
-        <v>106</v>
-      </c>
-      <c r="M1" s="22" t="s">
-        <v>107</v>
+    </row>
+    <row r="31" spans="1:13" s="44" customFormat="1" ht="36">
+      <c r="A31" s="42" t="s">
+        <v>276</v>
+      </c>
+      <c r="B31" s="43" t="s">
+        <v>98</v>
+      </c>
+      <c r="C31" s="43" t="s">
+        <v>277</v>
+      </c>
+      <c r="D31" s="43" t="s">
+        <v>278</v>
+      </c>
+      <c r="E31" s="43" t="s">
+        <v>279</v>
+      </c>
+      <c r="F31" s="43" t="s">
+        <v>144</v>
+      </c>
+      <c r="G31" s="43" t="s">
+        <v>280</v>
+      </c>
+      <c r="H31" s="56" t="s">
+        <v>280</v>
+      </c>
+      <c r="I31" s="58" t="s">
+        <v>122</v>
+      </c>
+      <c r="J31" s="43" t="s">
+        <v>123</v>
+      </c>
+      <c r="K31" s="43" t="s">
+        <v>123</v>
+      </c>
+      <c r="L31" s="96" t="s">
+        <v>123</v>
+      </c>
+      <c r="M31" s="115" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" s="44" customFormat="1" ht="36">
+      <c r="A32" s="42" t="s">
+        <v>281</v>
+      </c>
+      <c r="B32" s="43" t="s">
+        <v>98</v>
+      </c>
+      <c r="C32" s="43" t="s">
+        <v>277</v>
+      </c>
+      <c r="D32" s="43" t="s">
+        <v>282</v>
+      </c>
+      <c r="E32" s="43" t="s">
+        <v>283</v>
+      </c>
+      <c r="F32" s="43" t="s">
+        <v>144</v>
+      </c>
+      <c r="G32" s="43" t="s">
+        <v>284</v>
+      </c>
+      <c r="H32" s="56" t="s">
+        <v>284</v>
+      </c>
+      <c r="I32" s="58" t="s">
+        <v>122</v>
+      </c>
+      <c r="J32" s="43" t="s">
+        <v>123</v>
+      </c>
+      <c r="K32" s="43" t="s">
+        <v>123</v>
+      </c>
+      <c r="L32" s="96" t="s">
+        <v>123</v>
+      </c>
+      <c r="M32" s="115" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA5B6BCA-3039-4579-A5CF-7044720D131E}">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="27.140625" customWidth="1"/>
+    <col min="3" max="3" width="37" customWidth="1"/>
+    <col min="4" max="4" width="27.42578125" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" customWidth="1"/>
+    <col min="6" max="6" width="22.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="78" t="s">
+        <v>285</v>
+      </c>
+      <c r="B1" s="81" t="s">
+        <v>286</v>
+      </c>
+      <c r="C1" s="81" t="s">
+        <v>287</v>
+      </c>
+      <c r="D1" s="81" t="s">
+        <v>288</v>
+      </c>
+      <c r="E1" s="81" t="s">
+        <v>289</v>
+      </c>
+      <c r="F1" s="81" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="131.25" customHeight="1">
+      <c r="A2" s="80" t="s">
+        <v>291</v>
+      </c>
+      <c r="B2" s="116" t="s">
+        <v>292</v>
+      </c>
+      <c r="C2" s="79" t="s">
+        <v>293</v>
+      </c>
+      <c r="D2" s="117" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="82" t="s">
+        <v>123</v>
+      </c>
+      <c r="F2" s="83" t="s">
+        <v>294</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B29EFCF7-3378-4713-B577-863F61F08A5A}">
+  <dimension ref="A1:F32"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.5703125" customWidth="1"/>
+    <col min="2" max="2" width="26.140625" customWidth="1"/>
+    <col min="3" max="3" width="22.42578125" customWidth="1"/>
+    <col min="4" max="4" width="24.5703125" customWidth="1"/>
+    <col min="6" max="6" width="23.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="45" t="s">
+        <v>295</v>
+      </c>
+      <c r="B1" s="46" t="s">
+        <v>296</v>
+      </c>
+      <c r="C1" s="46" t="s">
+        <v>297</v>
+      </c>
+      <c r="D1" s="46" t="s">
+        <v>298</v>
+      </c>
+      <c r="E1" s="46" t="s">
+        <v>299</v>
+      </c>
+      <c r="F1" s="46" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="44" t="s">
+        <v>301</v>
+      </c>
+      <c r="B2" s="44" t="s">
+        <v>302</v>
+      </c>
+      <c r="C2" s="44" t="s">
+        <v>65</v>
+      </c>
+      <c r="D2" s="61" t="s">
+        <v>115</v>
+      </c>
+      <c r="E2" s="47" t="s">
+        <v>303</v>
+      </c>
+      <c r="F2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="D3" s="62" t="s">
+        <v>124</v>
+      </c>
+      <c r="E3" s="48" t="s">
+        <v>303</v>
+      </c>
+      <c r="F3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="44" t="s">
+        <v>304</v>
+      </c>
+      <c r="B4" s="44" t="s">
+        <v>305</v>
+      </c>
+      <c r="C4" s="44" t="s">
+        <v>70</v>
+      </c>
+      <c r="D4" s="62" t="s">
+        <v>129</v>
+      </c>
+      <c r="E4" s="48" t="s">
+        <v>303</v>
+      </c>
+      <c r="F4" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="D5" s="62" t="s">
+        <v>135</v>
+      </c>
+      <c r="E5" s="47" t="s">
+        <v>303</v>
+      </c>
+      <c r="F5" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="D6" s="62" t="s">
+        <v>140</v>
+      </c>
+      <c r="E6" s="47" t="s">
+        <v>303</v>
+      </c>
+      <c r="F6" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="44" t="s">
+        <v>306</v>
+      </c>
+      <c r="B7" s="44" t="s">
+        <v>307</v>
+      </c>
+      <c r="C7" s="44" t="s">
+        <v>74</v>
+      </c>
+      <c r="D7" s="61" t="s">
+        <v>146</v>
+      </c>
+      <c r="E7" s="47" t="s">
+        <v>303</v>
+      </c>
+      <c r="F7" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="D8" s="62" t="s">
+        <v>152</v>
+      </c>
+      <c r="E8" s="47" t="s">
+        <v>303</v>
+      </c>
+      <c r="F8" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="D9" s="62" t="s">
+        <v>159</v>
+      </c>
+      <c r="E9" s="47" t="s">
+        <v>303</v>
+      </c>
+      <c r="F9" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="D10" s="62" t="s">
+        <v>163</v>
+      </c>
+      <c r="E10" s="47" t="s">
+        <v>303</v>
+      </c>
+      <c r="F10" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="D11" s="62" t="s">
+        <v>169</v>
+      </c>
+      <c r="E11" s="47" t="s">
+        <v>303</v>
+      </c>
+      <c r="F11" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="44" t="s">
+        <v>308</v>
+      </c>
+      <c r="B12" s="44" t="s">
+        <v>309</v>
+      </c>
+      <c r="C12" s="44" t="s">
+        <v>78</v>
+      </c>
+      <c r="D12" s="62" t="s">
+        <v>175</v>
+      </c>
+      <c r="E12" s="47" t="s">
+        <v>303</v>
+      </c>
+      <c r="F12" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="D13" s="62" t="s">
+        <v>180</v>
+      </c>
+      <c r="E13" s="47" t="s">
+        <v>303</v>
+      </c>
+      <c r="F13" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="D14" s="62" t="s">
+        <v>186</v>
+      </c>
+      <c r="E14" s="47" t="s">
+        <v>303</v>
+      </c>
+      <c r="F14" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="D15" s="62" t="s">
+        <v>189</v>
+      </c>
+      <c r="E15" s="60" t="s">
+        <v>310</v>
+      </c>
+      <c r="F15" s="44" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="44" t="s">
+        <v>311</v>
+      </c>
+      <c r="B16" s="44" t="s">
+        <v>312</v>
+      </c>
+      <c r="C16" s="44" t="s">
+        <v>82</v>
+      </c>
+      <c r="D16" s="61" t="s">
+        <v>196</v>
+      </c>
+      <c r="E16" s="47" t="s">
+        <v>303</v>
+      </c>
+      <c r="F16" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="D17" s="62" t="s">
+        <v>201</v>
+      </c>
+      <c r="E17" s="47" t="s">
+        <v>303</v>
+      </c>
+      <c r="F17" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="D18" s="62" t="s">
+        <v>206</v>
+      </c>
+      <c r="E18" s="47" t="s">
+        <v>303</v>
+      </c>
+      <c r="F18" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="D19" s="62" t="s">
+        <v>212</v>
+      </c>
+      <c r="E19" s="47" t="s">
+        <v>303</v>
+      </c>
+      <c r="F19" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="44" t="s">
+        <v>313</v>
+      </c>
+      <c r="B20" s="44" t="s">
+        <v>314</v>
+      </c>
+      <c r="C20" s="44" t="s">
+        <v>86</v>
+      </c>
+      <c r="D20" s="62" t="s">
+        <v>217</v>
+      </c>
+      <c r="E20" s="47" t="s">
+        <v>303</v>
+      </c>
+      <c r="F20" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="D21" s="62" t="s">
+        <v>223</v>
+      </c>
+      <c r="E21" s="47" t="s">
+        <v>303</v>
+      </c>
+      <c r="F21" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="D22" s="62" t="s">
+        <v>228</v>
+      </c>
+      <c r="E22" s="47" t="s">
+        <v>303</v>
+      </c>
+      <c r="F22" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="D23" s="62" t="s">
+        <v>233</v>
+      </c>
+      <c r="E23" s="47" t="s">
+        <v>303</v>
+      </c>
+      <c r="F23" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="44" t="s">
+        <v>315</v>
+      </c>
+      <c r="B24" s="44" t="s">
+        <v>316</v>
+      </c>
+      <c r="C24" s="44" t="s">
+        <v>90</v>
+      </c>
+      <c r="D24" s="61" t="s">
+        <v>237</v>
+      </c>
+      <c r="E24" s="47" t="s">
+        <v>303</v>
+      </c>
+      <c r="F24" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="D25" s="62" t="s">
+        <v>243</v>
+      </c>
+      <c r="E25" s="47" t="s">
+        <v>303</v>
+      </c>
+      <c r="F25" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="D26" s="62" t="s">
+        <v>249</v>
+      </c>
+      <c r="E26" s="47" t="s">
+        <v>303</v>
+      </c>
+      <c r="F26" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" s="44" t="s">
+        <v>317</v>
+      </c>
+      <c r="B27" s="44" t="s">
+        <v>318</v>
+      </c>
+      <c r="C27" s="44" t="s">
+        <v>94</v>
+      </c>
+      <c r="D27" s="62" t="s">
+        <v>255</v>
+      </c>
+      <c r="E27" s="47" t="s">
+        <v>303</v>
+      </c>
+      <c r="F27" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="D28" s="62" t="s">
+        <v>261</v>
+      </c>
+      <c r="E28" s="47" t="s">
+        <v>303</v>
+      </c>
+      <c r="F28" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="D29" s="62" t="s">
+        <v>266</v>
+      </c>
+      <c r="E29" s="47" t="s">
+        <v>303</v>
+      </c>
+      <c r="F29" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="44" t="s">
+        <v>319</v>
+      </c>
+      <c r="B30" s="44" t="s">
+        <v>320</v>
+      </c>
+      <c r="C30" s="44" t="s">
+        <v>98</v>
+      </c>
+      <c r="D30" s="61" t="s">
+        <v>270</v>
+      </c>
+      <c r="E30" s="47" t="s">
+        <v>303</v>
+      </c>
+      <c r="F30" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="D31" s="62" t="s">
+        <v>276</v>
+      </c>
+      <c r="E31" s="47" t="s">
+        <v>303</v>
+      </c>
+      <c r="F31" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="D32" s="62" t="s">
+        <v>281</v>
+      </c>
+      <c r="E32" s="47" t="s">
+        <v>303</v>
+      </c>
+      <c r="F32" t="s">
+        <v>144</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F896AF1F-45AF-40E9-AE2E-C856BCCB02E2}">
+  <dimension ref="A1:I12"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="34.28515625" customWidth="1"/>
+    <col min="2" max="2" width="55.7109375" customWidth="1"/>
+    <col min="3" max="3" width="26.85546875" customWidth="1"/>
+    <col min="4" max="4" width="17.140625" customWidth="1"/>
+    <col min="5" max="5" width="12.85546875" customWidth="1"/>
+    <col min="6" max="6" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="21.7109375" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" customWidth="1"/>
+    <col min="9" max="9" width="21.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="20.25">
+      <c r="A1" s="84" t="s">
+        <v>321</v>
+      </c>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
+      <c r="H1" s="85"/>
+      <c r="I1" s="86"/>
+    </row>
+    <row r="2" spans="1:9" ht="24">
+      <c r="A2" s="118" t="s">
+        <v>322</v>
+      </c>
+      <c r="B2" s="119" t="s">
+        <v>323</v>
+      </c>
+      <c r="C2" s="119" t="s">
+        <v>324</v>
+      </c>
+      <c r="D2" s="119" t="s">
+        <v>325</v>
+      </c>
+      <c r="E2" s="119" t="s">
+        <v>326</v>
+      </c>
+      <c r="F2" s="119" t="s">
+        <v>327</v>
+      </c>
+      <c r="G2" s="119" t="s">
+        <v>328</v>
+      </c>
+      <c r="H2" s="119" t="s">
+        <v>329</v>
+      </c>
+      <c r="I2" s="119" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="87" t="s">
+        <v>331</v>
+      </c>
+      <c r="B3" s="77" t="s">
+        <v>332</v>
+      </c>
+      <c r="C3" s="63">
+        <v>2</v>
+      </c>
+      <c r="D3" s="63">
+        <v>2</v>
+      </c>
+      <c r="E3" s="63">
+        <v>0</v>
+      </c>
+      <c r="F3" s="63">
+        <v>2</v>
+      </c>
+      <c r="G3" s="65">
+        <v>1</v>
+      </c>
+      <c r="H3" s="65">
+        <v>0</v>
+      </c>
+      <c r="I3" s="65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="14.25">
+      <c r="A4" s="88"/>
+      <c r="B4" s="69" t="s">
+        <v>333</v>
+      </c>
+      <c r="C4" s="64">
+        <v>3</v>
+      </c>
+      <c r="D4" s="64">
+        <v>3</v>
+      </c>
+      <c r="E4" s="64">
+        <v>0</v>
+      </c>
+      <c r="F4" s="64">
+        <v>3</v>
+      </c>
+      <c r="G4" s="66">
+        <v>1</v>
+      </c>
+      <c r="H4" s="66">
+        <v>0</v>
+      </c>
+      <c r="I4" s="66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="14.25">
+      <c r="A5" s="88"/>
+      <c r="B5" s="70" t="s">
+        <v>334</v>
+      </c>
+      <c r="C5" s="63">
+        <v>5</v>
+      </c>
+      <c r="D5" s="63">
+        <v>5</v>
+      </c>
+      <c r="E5" s="63">
+        <v>0</v>
+      </c>
+      <c r="F5" s="63">
+        <v>5</v>
+      </c>
+      <c r="G5" s="65">
+        <v>1</v>
+      </c>
+      <c r="H5" s="65">
+        <v>0</v>
+      </c>
+      <c r="I5" s="65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="14.25">
+      <c r="A6" s="88"/>
+      <c r="B6" s="67" t="s">
+        <v>335</v>
+      </c>
+      <c r="C6" s="64">
+        <v>4</v>
+      </c>
+      <c r="D6" s="64">
+        <v>3</v>
+      </c>
+      <c r="E6" s="64">
+        <v>1</v>
+      </c>
+      <c r="F6" s="64">
+        <v>4</v>
+      </c>
+      <c r="G6" s="66">
+        <v>0.75</v>
+      </c>
+      <c r="H6" s="66">
+        <v>0.25</v>
+      </c>
+      <c r="I6" s="66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="14.25">
+      <c r="A7" s="88"/>
+      <c r="B7" s="71" t="s">
+        <v>336</v>
+      </c>
+      <c r="C7" s="63">
+        <v>4</v>
+      </c>
+      <c r="D7" s="63">
+        <v>4</v>
+      </c>
+      <c r="E7" s="63">
+        <v>0</v>
+      </c>
+      <c r="F7" s="63">
+        <v>4</v>
+      </c>
+      <c r="G7" s="65">
+        <v>1</v>
+      </c>
+      <c r="H7" s="65">
+        <v>0</v>
+      </c>
+      <c r="I7" s="65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="14.25">
+      <c r="A8" s="88"/>
+      <c r="B8" s="69" t="s">
+        <v>337</v>
+      </c>
+      <c r="C8" s="64">
+        <v>4</v>
+      </c>
+      <c r="D8" s="64">
+        <v>4</v>
+      </c>
+      <c r="E8" s="64">
+        <v>0</v>
+      </c>
+      <c r="F8" s="64">
+        <v>4</v>
+      </c>
+      <c r="G8" s="66">
+        <v>1</v>
+      </c>
+      <c r="H8" s="66">
+        <v>0</v>
+      </c>
+      <c r="I8" s="66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="14.25">
+      <c r="A9" s="88"/>
+      <c r="B9" s="70" t="s">
+        <v>338</v>
+      </c>
+      <c r="C9" s="63">
+        <v>3</v>
+      </c>
+      <c r="D9" s="63">
+        <v>3</v>
+      </c>
+      <c r="E9" s="63">
+        <v>0</v>
+      </c>
+      <c r="F9" s="63">
+        <v>3</v>
+      </c>
+      <c r="G9" s="65">
+        <v>1</v>
+      </c>
+      <c r="H9" s="65">
+        <v>0</v>
+      </c>
+      <c r="I9" s="65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="14.25">
+      <c r="A10" s="88"/>
+      <c r="B10" s="69" t="s">
+        <v>339</v>
+      </c>
+      <c r="C10" s="64">
+        <v>3</v>
+      </c>
+      <c r="D10" s="64">
+        <v>3</v>
+      </c>
+      <c r="E10" s="64">
+        <v>0</v>
+      </c>
+      <c r="F10" s="64">
+        <v>3</v>
+      </c>
+      <c r="G10" s="66">
+        <v>1</v>
+      </c>
+      <c r="H10" s="66">
+        <v>0</v>
+      </c>
+      <c r="I10" s="66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="14.25">
+      <c r="A11" s="89"/>
+      <c r="B11" s="68" t="s">
+        <v>340</v>
+      </c>
+      <c r="C11" s="63">
+        <v>3</v>
+      </c>
+      <c r="D11" s="63">
+        <v>3</v>
+      </c>
+      <c r="E11" s="63">
+        <v>0</v>
+      </c>
+      <c r="F11" s="63">
+        <v>3</v>
+      </c>
+      <c r="G11" s="65">
+        <v>1</v>
+      </c>
+      <c r="H11" s="65">
+        <v>0</v>
+      </c>
+      <c r="I11" s="65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="75" t="s">
+        <v>341</v>
+      </c>
+      <c r="B12" s="76" t="s">
+        <v>342</v>
+      </c>
+      <c r="C12" s="72">
+        <v>31</v>
+      </c>
+      <c r="D12" s="73">
+        <v>30</v>
+      </c>
+      <c r="E12" s="73">
+        <v>1</v>
+      </c>
+      <c r="F12" s="73">
+        <v>31</v>
+      </c>
+      <c r="G12" s="74">
+        <v>0.97</v>
+      </c>
+      <c r="H12" s="74">
+        <v>0.03</v>
+      </c>
+      <c r="I12" s="74">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:A11"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>